--- a/翻訳表_忍者タイプ診断アプリ.xlsx
+++ b/翻訳表_忍者タイプ診断アプリ.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">全十問の問いに答えよ。
 虚無僧、出家、山伏、商人、刺客——
 十二の忍びの道の中から、
-お前の内に眠る本性を暴き出す。</t>
+内に眠る本性を暴き出す。</t>
   </si>
   <si>
     <t xml:space="preserve">Answer all ten questions.
@@ -111,7 +111,7 @@
     <t>ResultCard</t>
   </si>
   <si>
-    <t>お前の忍びの道は――</t>
+    <t>忍びの道は――</t>
   </si>
   <si>
     <t>Thy path of shinobi is —</t>
@@ -339,10 +339,10 @@
     <t>常の形</t>
   </si>
   <si>
-    <t>Tsunenokatachi</t>
-  </si>
-  <si>
-    <t>The Ordinary Form</t>
+    <t>Tsunenokata</t>
+  </si>
+  <si>
+    <t>The Peasant</t>
   </si>
   <si>
     <t>擬態・堅実・目立たなさ</t>
@@ -840,7 +840,7 @@
     <t>buke_2</t>
   </si>
   <si>
-    <t>休みの日をどう過ごしますか?</t>
+    <t>休みの日を、どう過ごす?</t>
   </si>
   <si>
     <t>How do you spend your days off?</t>
@@ -885,7 +885,7 @@
     <t>buke_3</t>
   </si>
   <si>
-    <t>空いた時間に何を究めますか?</t>
+    <t>空いた時間に、何を究める?</t>
   </si>
   <si>
     <t>What do you devote your spare time to mastering?</t>
@@ -1098,7 +1098,7 @@
     <t>shomin_2</t>
   </si>
   <si>
-    <t>忍びとして、お前が得意なのは?</t>
+    <t>忍びとして、得意なのは?</t>
   </si>
   <si>
     <t>As a shinobi, what are you good at?</t>
@@ -1809,7 +1809,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2167,7 +2167,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2578,7 +2578,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2769,7 +2769,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2960,7 +2960,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3151,6 +3151,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/翻訳表_忍者タイプ診断アプリ.xlsx
+++ b/翻訳表_忍者タイプ診断アプリ.xlsx
@@ -498,7 +498,7 @@
     <t>c1b</t>
   </si>
   <si>
-    <t>心を落ち着け、自分の調子を整えてから取りかかる</t>
+    <t>心を落ち着かせ、自分の調子を整えてから取りかかる</t>
   </si>
   <si>
     <t>Calm your mind and get yourself in the right state before starting.</t>

--- a/翻訳表_忍者タイプ診断アプリ.xlsx
+++ b/翻訳表_忍者タイプ診断アプリ.xlsx
@@ -933,37 +933,37 @@
     <t>jisha_1a</t>
   </si>
   <si>
-    <t>托鉢の僧を装い、里の中に紛れ込む</t>
-  </si>
-  <si>
-    <t>Disguise yourself as a begging monk and slip into the village.</t>
+    <t>見返りを求めず、困っている人を助けながら入り込む</t>
+  </si>
+  <si>
+    <t>Expect nothing in return, and slip in by helping people in need.</t>
   </si>
   <si>
     <t>jisha_1b</t>
   </si>
   <si>
-    <t>経を唱えながら、寺社の一員として入り込む</t>
-  </si>
-  <si>
-    <t>Chant sutras and enter as one of the temple's own.</t>
+    <t>争いを避け、穏やかな態度で人々の中へ入り込む</t>
+  </si>
+  <si>
+    <t>Avoid conflict and enter among the people with a gentle manner.</t>
   </si>
   <si>
     <t>jisha_1c</t>
   </si>
   <si>
-    <t>山伏の姿で、堂々と山を越えて訪れる</t>
-  </si>
-  <si>
-    <t>Come openly over the mountain, dressed as a yamabushi.</t>
+    <t>険しい道のりも自分の足で越え、正面から訪れる</t>
+  </si>
+  <si>
+    <t>Cross even the roughest road on your own two feet, and arrive openly.</t>
   </si>
   <si>
     <t>jisha_1d</t>
   </si>
   <si>
-    <t>法螺貝を吹き鳴らしながら、修行の一団として入り込む</t>
-  </si>
-  <si>
-    <t>Blow the conch-shell horn and enter as part of a band of ascetics.</t>
+    <t>厳しい道を仲間とともに歩み、一団として入り込む</t>
+  </si>
+  <si>
+    <t>Walk the hard road together with your companions, and enter as one group.</t>
   </si>
   <si>
     <t>jisha_2</t>
@@ -978,10 +978,10 @@
     <t>jisha_2a</t>
   </si>
   <si>
-    <t>静かに読経し、自分の心と向き合う</t>
-  </si>
-  <si>
-    <t>Quietly chant a sutra and face your own heart.</t>
+    <t>静かに目を閉じ、自分の心と向き合う</t>
+  </si>
+  <si>
+    <t>Quietly close your eyes and face your own heart.</t>
   </si>
   <si>
     <t>jisha_2b</t>
@@ -996,10 +996,10 @@
     <t>jisha_2c</t>
   </si>
   <si>
-    <t>法螺貝を吹き鳴らし、呼吸を整える</t>
-  </si>
-  <si>
-    <t>Blow the conch-shell horn and steady your breathing.</t>
+    <t>深く息を整え、体に意識を向けて落ち着く</t>
+  </si>
+  <si>
+    <t>Steady your breath deeply and settle by turning your attention to your body.</t>
   </si>
   <si>
     <t>jisha_2d</t>
@@ -1023,28 +1023,28 @@
     <t>jisha_3a</t>
   </si>
   <si>
-    <t>数珠を手に、人のために己を律して動く</t>
-  </si>
-  <si>
-    <t>Prayer beads in hand, discipline yourself and act for others.</t>
+    <t>人のために、己を律して動く</t>
+  </si>
+  <si>
+    <t>Discipline yourself and act for the sake of others.</t>
   </si>
   <si>
     <t>jisha_3b</t>
   </si>
   <si>
-    <t>静かな読経で、欲や迷いに振り回されぬ心を示す</t>
-  </si>
-  <si>
-    <t>Show, through quiet chanting, a heart unmoved by desire or doubt.</t>
+    <t>静けさの中で、欲や迷いに振り回されぬ心を示す</t>
+  </si>
+  <si>
+    <t>Show, in stillness, a heart unmoved by desire or doubt.</t>
   </si>
   <si>
     <t>jisha_3c</t>
   </si>
   <si>
-    <t>法螺貝を吹き鳴らし、苦しい山道でも前に進み続ける</t>
-  </si>
-  <si>
-    <t>Blow the conch-shell horn and keep pressing on, even up the hardest mountain paths.</t>
+    <t>苦しい道のりでも、前に進み続ける</t>
+  </si>
+  <si>
+    <t>Keep pressing on, even along the hardest road.</t>
   </si>
   <si>
     <t>jisha_3d</t>
@@ -1062,10 +1062,10 @@
     <t>shomin_1a</t>
   </si>
   <si>
-    <t>一般庶民になりきって、紛れ込む</t>
-  </si>
-  <si>
-    <t>Pass yourself off completely as an ordinary commoner and slip in.</t>
+    <t>現地の人に紛れる</t>
+  </si>
+  <si>
+    <t>Blend in with the locals.</t>
   </si>
   <si>
     <t>shomin_1b</t>
